--- a/docs/oc-regiones/insumos-y-dispositivos-medicos/tarapaca.xlsx
+++ b/docs/oc-regiones/insumos-y-dispositivos-medicos/tarapaca.xlsx
@@ -623,7 +623,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1493,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1558,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1745,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1810,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1875,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2062,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2127,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2192,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2318,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2505,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2692,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2818,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3066,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3131,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3257,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3505,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3570,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3757,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3883,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +3948,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4440,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4566,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4692,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4757,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4822,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5009,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5135,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5200,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5387,11 @@
           <t>76.399.126-1</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5452,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5578,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5704,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6074,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6139,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6326,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6391,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6517,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6643,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6708,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6773,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +6899,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7025,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7151,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7338,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7403,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7590,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7777,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +7903,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7968,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8155,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8220,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8468,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8594,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8659,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +8724,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9033,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9220,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9407,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9472,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9659,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9785,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +9972,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10098,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10163,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10350,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10476,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10663,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +10850,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11281,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11407,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11533,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11598,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11663,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +11850,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +11915,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12041,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12350,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12476,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12541,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12667,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +12732,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +12797,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +12923,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13049,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13236,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13362,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13427,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13614,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13679,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +13866,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14053,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14179,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14305,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14370,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14435,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14622,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +14687,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +14874,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15000,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +15492,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +15740,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15805,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +15931,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +15996,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16061,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16126,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16191,11 @@
           <t>77.261.932-4</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16378,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +16565,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +16630,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16817,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17004,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17191,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17256,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17321,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +17569,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17634,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18004,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18069,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18134,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +18443,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18630,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18695,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19004,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19069,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19134,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19260,11 @@
           <t>77.261.932-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19325,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +19451,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19516,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +19703,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +19768,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19833,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +19959,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20085,11 @@
           <t>76.271.360-8</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20150,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20215,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +20341,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20406,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +20593,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +20658,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +20784,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20849,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20914,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21040,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +21349,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +21658,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +21906,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +21971,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22158,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22223,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +22288,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +22353,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +22418,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +22483,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +22975,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +23223,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +23349,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +23414,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +23601,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +23666,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +23731,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +23857,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +23983,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24048,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +24174,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +24239,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +24304,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +24491,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +24678,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +24804,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +24869,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +24995,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25060,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25125,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +25190,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +25438,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +25503,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +25568,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26060,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +26247,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +26373,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +26560,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +26747,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +26995,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27060,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +27125,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +27312,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +27499,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +27564,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +27629,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +27694,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +27942,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28007,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +28072,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +28198,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +28324,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +28450,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +28515,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +28763,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +28828,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +28893,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +28958,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +29084,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +29210,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +29580,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +29645,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +29710,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +29775,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +29840,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +29966,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +30153,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +30218,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +30466,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +30531,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +30657,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +30783,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +30909,11 @@
           <t>77.342.295-8</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +31035,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +31100,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +31165,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +31230,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +31295,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +31360,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +31425,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +31551,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +31616,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +31864,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +31990,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +32055,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +32120,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +32185,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +32372,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +32498,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +32624,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +32750,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +32998,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +33185,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +33494,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +33742,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +33929,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +33994,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +34120,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +34185,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +34555,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +34986,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34173,7 +35173,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34356,7 +35360,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34600,7 +35608,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34783,7 +35795,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34844,7 +35860,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35088,7 +36108,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35210,7 +36234,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35515,7 +36543,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35637,7 +36669,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36064,7 +37100,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36125,7 +37165,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36247,7 +37291,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36430,7 +37478,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36613,7 +37665,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K593" t="inlineStr"/>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L593" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36674,7 +37730,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36796,7 +37856,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36918,7 +37982,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37101,7 +38169,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37223,7 +38295,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37345,7 +38421,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37528,7 +38608,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38077,7 +39161,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38138,7 +39226,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38199,7 +39291,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38321,7 +39417,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38565,7 +39665,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38626,7 +39730,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38687,7 +39795,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38809,7 +39921,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38870,7 +39986,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39114,7 +40234,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39175,7 +40299,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39297,7 +40425,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39419,7 +40551,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39480,7 +40616,11 @@
           <t>77.054.075-5</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39541,7 +40681,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39663,7 +40807,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39724,7 +40872,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39785,7 +40937,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39907,7 +41063,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40029,7 +41189,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40151,7 +41315,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40212,7 +41380,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40334,7 +41506,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40517,7 +41693,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40761,7 +41941,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40822,7 +42006,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40883,7 +42071,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40944,7 +42136,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41005,7 +42201,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41127,7 +42327,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41249,7 +42453,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41554,7 +42762,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41859,7 +43071,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42042,7 +43258,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42347,7 +43567,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42591,7 +43815,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42652,7 +43880,11 @@
           <t>76.780.759-7</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42713,7 +43945,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42835,7 +44071,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43201,7 +44441,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43750,7 +44994,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43811,7 +45059,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43872,7 +45124,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43933,7 +45189,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43994,7 +45254,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44055,7 +45319,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44116,7 +45384,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44177,7 +45449,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44360,7 +45636,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44421,7 +45701,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44726,7 +46010,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44787,7 +46075,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44970,7 +46262,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45153,7 +46449,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45336,7 +46636,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45641,7 +46945,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45763,7 +47071,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45824,7 +47136,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45946,7 +47262,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46068,7 +47388,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K748" t="inlineStr"/>
+      <c r="K748" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L748" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46129,7 +47453,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46434,7 +47762,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46556,7 +47888,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46678,7 +48014,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46861,7 +48201,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47105,7 +48449,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47166,7 +48514,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47227,7 +48579,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47593,7 +48949,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47715,7 +49075,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47959,7 +49323,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48325,7 +49693,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48386,7 +49758,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48630,7 +50006,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48813,7 +50193,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48935,7 +50319,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49118,7 +50506,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K798" t="inlineStr"/>
+      <c r="K798" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L798" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49240,7 +50632,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49484,7 +50880,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49545,7 +50945,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49606,7 +51010,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49789,7 +51197,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49911,7 +51323,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49972,7 +51388,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K812" t="inlineStr"/>
+      <c r="K812" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L812" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50094,7 +51514,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50216,7 +51640,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K816" t="inlineStr"/>
+      <c r="K816" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L816" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50277,7 +51705,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50460,7 +51892,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50643,7 +52079,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50765,7 +52205,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51070,7 +52514,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K830" t="inlineStr"/>
+      <c r="K830" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L830" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51253,7 +52701,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51436,7 +52888,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51558,7 +53014,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51680,7 +53140,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51863,7 +53327,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51985,7 +53453,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K845" t="inlineStr"/>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L845" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52229,7 +53701,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52351,7 +53827,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52412,7 +53892,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K852" t="inlineStr"/>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L852" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52534,7 +54018,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52595,7 +54083,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52656,7 +54148,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52778,7 +54274,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52839,7 +54339,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52900,7 +54404,11 @@
           <t>99.569.670-3</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52961,7 +54469,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53144,7 +54656,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53327,7 +54843,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L867" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53510,7 +55030,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53693,7 +55217,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53998,7 +55526,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K878" t="inlineStr"/>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L878" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54059,7 +55591,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54303,7 +55839,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54486,7 +56026,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54547,7 +56091,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54608,7 +56156,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K888" t="inlineStr"/>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L888" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54669,7 +56221,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54730,7 +56286,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55096,7 +56656,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55218,7 +56782,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55279,7 +56847,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55340,7 +56912,11 @@
           <t>76.116.604-2</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55401,7 +56977,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55462,7 +57042,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55523,7 +57107,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55584,7 +57172,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55645,7 +57237,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K905" t="inlineStr"/>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L905" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55706,7 +57302,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55767,7 +57367,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55889,7 +57493,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55950,7 +57558,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56011,7 +57623,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56133,7 +57749,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56194,7 +57814,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56316,7 +57940,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56682,7 +58310,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56743,7 +58375,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56926,7 +58562,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57353,7 +58993,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K933" t="inlineStr"/>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L933" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57475,7 +59119,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K935" t="inlineStr"/>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L935" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57658,7 +59306,11 @@
           <t>77.561.431-5</t>
         </is>
       </c>
-      <c r="K938" t="inlineStr"/>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L938" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58146,7 +59798,11 @@
           <t>86.397.000-8</t>
         </is>
       </c>
-      <c r="K946" t="inlineStr"/>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L946" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58207,7 +59863,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K947" t="inlineStr"/>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L947" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58451,7 +60111,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K951" t="inlineStr"/>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L951" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58939,7 +60603,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K959" t="inlineStr"/>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L959" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59427,7 +61095,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K967" t="inlineStr"/>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L967" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59671,7 +61343,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K971" t="inlineStr"/>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L971" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59976,7 +61652,11 @@
           <t>77.910.467-2</t>
         </is>
       </c>
-      <c r="K976" t="inlineStr"/>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L976" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60159,7 +61839,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K979" t="inlineStr"/>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L979" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60220,7 +61904,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K980" t="inlineStr"/>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L980" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60464,7 +62152,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K984" t="inlineStr"/>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L984" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60586,7 +62278,11 @@
           <t>96.756.540-7</t>
         </is>
       </c>
-      <c r="K986" t="inlineStr"/>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L986" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60708,7 +62404,11 @@
           <t>77.305.553-K</t>
         </is>
       </c>
-      <c r="K988" t="inlineStr"/>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L988" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60769,7 +62469,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K989" t="inlineStr"/>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L989" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60891,7 +62595,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K991" t="inlineStr"/>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L991" t="inlineStr">
         <is>
           <t>USD</t>
@@ -60952,7 +62660,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K992" t="inlineStr"/>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L992" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61013,7 +62725,11 @@
           <t>93.366.000-1</t>
         </is>
       </c>
-      <c r="K993" t="inlineStr"/>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L993" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61074,7 +62790,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K994" t="inlineStr"/>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L994" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61257,7 +62977,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K997" t="inlineStr"/>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L997" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61501,7 +63225,11 @@
           <t>81.210.400-4</t>
         </is>
       </c>
-      <c r="K1001" t="inlineStr"/>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1001" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61562,7 +63290,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K1002" t="inlineStr"/>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1002" t="inlineStr">
         <is>
           <t>USD</t>
@@ -61623,7 +63355,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K1003" t="inlineStr"/>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L1003" t="inlineStr">
         <is>
           <t>USD</t>
